--- a/aa/xlsx/secrets-rotation-map.xlsx
+++ b/aa/xlsx/secrets-rotation-map.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IF-001, IF-003, IF-004</t>
+          <t>IF0, OAPI0, OAPI1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -532,21 +532,6 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>cmdb2label backend / server-side request memory</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>CMDBuild session policy</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Автоматически по истечению session / повторный login</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Требует согласования</t>
         </is>
       </c>
     </row>
@@ -558,7 +543,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IF-003</t>
+          <t>OAPI0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -584,21 +569,6 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>Browser / POST /resolve header</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>При ротации CMDB_LABELS_CSRF_SECRET</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Автоматически после смены секрета</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Требует согласования</t>
         </is>
       </c>
     </row>
@@ -610,7 +580,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IF-003</t>
+          <t>OAPI0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -636,21 +606,6 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>cmdb2label backend</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Требует согласования</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>По заявке / через deployment secret rotation</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Требует согласования</t>
         </is>
       </c>
     </row>
@@ -662,7 +617,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IF-004, IF-008</t>
+          <t>OAPI1, IF2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -688,21 +643,6 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>Node TLS через NODE_EXTRA_CA_CERTS; Docker build trust store при embedded mode</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Customer certificate rotation process</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Вручную / по заявке</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Требует согласования</t>
         </is>
       </c>
     </row>
@@ -714,7 +654,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IF-003, IF-004</t>
+          <t>OAPI0, OAPI1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -740,21 +680,6 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>cmdb2label backend</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>При изменении модели CMDBuild</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>По заявке / вместе с изменением модели</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Требует согласования</t>
         </is>
       </c>
     </row>
@@ -766,7 +691,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IF-007</t>
+          <t>OAPI2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -792,21 +717,6 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>CMDBuild custompages API</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Admin credential policy или session expiry</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Вручную / по заявке</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Требует согласования</t>
         </is>
       </c>
     </row>
@@ -818,7 +728,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IF-008</t>
+          <t>IF2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -844,21 +754,6 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>Registry/build platform</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Registry policy</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>По заявке / platform rotation</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Требует согласования</t>
         </is>
       </c>
     </row>
